--- a/templates/testfaelle_pacs008_comprehensive.xlsx
+++ b/templates/testfaelle_pacs008_comprehensive.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV51"/>
+  <dimension ref="A1:AV52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2274,7 +2274,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>Central</t>
@@ -8768,7 +8767,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
           <t>Central</t>
@@ -8999,6 +8997,173 @@
       <c r="AV51" t="inlineStr">
         <is>
           <t>BR-CBPR-PACS-010 in FR_EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TC-PCS-N21</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Negative: CRED ohne ChrgsInf</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Negative BR-CBPR-PACS-016 (CRED verlangt ChrgsInf)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NOK</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>CBPR+</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>UBSWCHZH80A</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>DEUTDEFFXXX</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>UBSWCHZH80A</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>DEUTDEFFXXX</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Muster AG</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Bahnhofstrasse</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Zurich</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>CH5604835012345678009</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>UBSWCHZH80A</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>DE Corp GmbH</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Kaiserstrasse</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>60311</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>DE89370400440532013000</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>DEUTDEFFXXX</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>INDA</t>
+        </is>
+      </c>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>CRED</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>Negative test case</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>BR-CBPR-PACS-016</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>Violation: CRED ohne ChrgsInf (BR-CBPR-PACS-016)</t>
         </is>
       </c>
     </row>

--- a/templates/testfaelle_pacs008_comprehensive.xlsx
+++ b/templates/testfaelle_pacs008_comprehensive.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV52"/>
+  <dimension ref="A1:AV54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9167,6 +9167,370 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TC-PCS-031</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CBPR+ EUR LI-&gt;HK mit 3 Intermediaries (Maximum)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Maximale Intermediary-Kette: LI-&gt;CH-&gt;DE-&gt;UK-&gt;HK</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>CBPR+</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BLFLLI2XXXX</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>HSBCHKHHXXX</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>BLFLLI2XXXX</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>HSBCHKHHXXX</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Vermoegensverwaltung Vaduz AG</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Herrengasse</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>9490</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Vaduz</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>LI2108800000023456789</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>BLFLLI2XXXX</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>UBSWCHZH80A</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>DEUTDEFFXXX</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>HBUKGB4BXXX</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Asia Pacific Trading Ltd</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Connaught Road Central</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>999077</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>400123456789</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>BBAN</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>HSBCHKHHXXX</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>250000.00</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>INDA</t>
+        </is>
+      </c>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>SHAR</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>Investment allocation Asia Q2 2026</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>Maximale 3-Intermediary-Chain: LI(LGT)-&gt;CH(UBS)-&gt;DE(DB)-&gt;UK(HSBC LDN)-&gt;HK(HSBC HK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TC-PCS-032</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CBPR+ EUR LI-&gt;HK, 3 Intermediaries via CH+DE+SG</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Maximale 3-Intermediary-Chain LI-&gt;CH-&gt;DE-&gt;SG-&gt;HK (alle via BIC)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>CBPR+</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BLFLLI2XXXX</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>HSBCHKHHXXX</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>BLFLLI2XXXX</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>HSBCHKHHXXX</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Stiftung Liechtenstein</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Staedtle</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>9490</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Vaduz</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>LI2108800000023456789</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>BLFLLI2XXXX</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>UBSWCHZH80A</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>DEUTDEFFXXX</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>SCBLSGSGXXX</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>HK Commodities Corp</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Queens Road</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>999077</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>HK</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>400987654321</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>BBAN</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>HSBCHKHHXXX</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>175000.00</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>INDA</t>
+        </is>
+      </c>
+      <c r="AN54" t="inlineStr">
+        <is>
+          <t>SHAR</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>Commodity settlement HK Q2</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>3-Intermediary-Chain via CH(UBS)-&gt;DE(DB)-&gt;SG(StanChart)-&gt;HK(HSBC)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
